--- a/Config/Luban/source/TbCharacter.xlsx
+++ b/Config/Luban/source/TbCharacter.xlsx
@@ -337,7 +337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:Z4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -353,6 +353,19 @@
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="15" max="15"/>
+    <col width="28" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="17" max="17"/>
+    <col width="28" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="28" customWidth="1" min="20" max="20"/>
+    <col width="28" customWidth="1" min="21" max="21"/>
+    <col width="28" customWidth="1" min="22" max="22"/>
+    <col width="28" customWidth="1" min="23" max="23"/>
+    <col width="28" customWidth="1" min="24" max="24"/>
+    <col width="28" customWidth="1" min="25" max="25"/>
+    <col width="28" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -421,6 +434,71 @@
           <t>gravity</t>
         </is>
       </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>shootMoveSpeed</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>moveAcceleration</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>swimAcceleration</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>wallSwimSpeed</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>wallGraceSeconds</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>wallProbeDistance</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>wallJumpSpeed</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>mantleSeconds</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>healthRecoverDelay</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>healthRecoverRate</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>swimHealthRecoverRate</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
+          <t>enemyInkDamageRate</t>
+        </is>
+      </c>
+      <c r="Z1" s="3" t="inlineStr">
+        <is>
+          <t>enemyInkHealthFloor</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -488,6 +566,71 @@
           <t>float</t>
         </is>
       </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Y2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
@@ -553,6 +696,71 @@
       <c r="M3" s="6" t="inlineStr">
         <is>
           <t>角色重力（米/秒²）</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>射击移动速度（米/秒）</t>
+        </is>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>人形加减速度（米/秒²）</t>
+        </is>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>潜墨加减速度（米/秒²）</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>墙游速度（米/秒）</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>墙面接缝接触容错（秒）</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>角色表面探测距离（米）</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>脱墙跳跃外推速度（米/秒）</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>墨水形态翻越时长（秒）</t>
+        </is>
+      </c>
+      <c r="V3" s="6" t="inlineStr">
+        <is>
+          <t>受伤后回血等待（秒）</t>
+        </is>
+      </c>
+      <c r="W3" s="6" t="inlineStr">
+        <is>
+          <t>普通回血（HP/秒）</t>
+        </is>
+      </c>
+      <c r="X3" s="6" t="inlineStr">
+        <is>
+          <t>己方潜墨回血（HP/秒）</t>
+        </is>
+      </c>
+      <c r="Y3" s="6" t="inlineStr">
+        <is>
+          <t>敌墨伤害（HP/秒）</t>
+        </is>
+      </c>
+      <c r="Z3" s="6" t="inlineStr">
+        <is>
+          <t>敌墨非致死生命下限（HP）</t>
         </is>
       </c>
     </row>
@@ -598,6 +806,45 @@
       <c r="M4" s="2" t="n">
         <v>22</v>
       </c>
+      <c r="N4" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="X4" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y4" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>60</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Luban/source/TbCharacter.xlsx
+++ b/Config/Luban/source/TbCharacter.xlsx
@@ -789,7 +789,7 @@
         <v>10</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>35</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>5</v>
